--- a/outputs/45896.xlsx
+++ b/outputs/45896.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t xml:space="preserve">Material</t>
   </si>
@@ -70,13 +70,25 @@
     <t xml:space="preserve">ABC1</t>
   </si>
   <si>
+    <t xml:space="preserve">31/12/2025,31/12/2024,31/12/2023</t>
+  </si>
+  <si>
     <t xml:space="preserve">ABC2</t>
   </si>
   <si>
+    <t xml:space="preserve">31/12/2022,31/12/2024</t>
+  </si>
+  <si>
     <t xml:space="preserve">ABC3</t>
   </si>
   <si>
+    <t xml:space="preserve">01/12/2024,31/12/2024</t>
+  </si>
+  <si>
     <t xml:space="preserve">ABC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31/12/2022</t>
   </si>
   <si>
     <t xml:space="preserve">ABC5</t>
@@ -213,56 +225,60 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -566,455 +582,446 @@
   <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="29.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="8.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="29.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="34.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="str">
+      <c r="B2" s="2" t="str">
         <f aca="false">_xlfn.IFNA(IF(COUNTIFS(ZORD!A:A,A2)&gt;1,"Yes",""),"")</f>
         <v>Yes</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="3" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A2,ZORD!A:A,ZORD!C:C),"")</f>
         <v>46022</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="11" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A2,ZORD!A:A,ZORD!E:E),"")</f>
         <v>460000001</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="2" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A2,ZORD!A:A,ZORD!D:D),"")</f>
         <v>200000001</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <f aca="false">IF(B2="Yes",_xlfn.XLOOKUP(A2,ZORD!A:A,ZORD!C:C,,,-1),"")</f>
         <v>45291</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="2" t="n">
         <f aca="false">IF(B2="Yes",_xlfn.XLOOKUP(A2,ZORD!A:A,ZORD!E:E,,,-1),"")</f>
         <v>460000000</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="2" t="n">
         <f aca="false">IF(B2="Yes",_xlfn.XLOOKUP(A2,ZORD!A:A,ZORD!D:D,,,-1),"")</f>
         <v>200000000</v>
       </c>
-      <c r="I2" s="11" t="str">
-        <f aca="false" t="array" ref="I2:I2">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(TEXT(IF(A2=ZORD!A:A,ZORD!C:C,""),"DD/MM/YYYY")))</f>
-        <v>31/12/2025,31/12/2024,31/12/2023</v>
-      </c>
-      <c r="J2" s="11" t="str">
+      <c r="I2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="12" t="str">
         <f aca="false" t="array" ref="J2:J2">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A2=ZORD!A:A,ZORD!D:D,"")))</f>
         <v>200000001,200000002,200000000</v>
       </c>
-      <c r="K2" s="11" t="str">
+      <c r="K2" s="12" t="str">
         <f aca="false" t="array" ref="K2:K2">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A2=ZORD!A:A,ZORD!E:E,"")))</f>
         <v>460000001,460000002,460000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="1" t="str">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="str">
         <f aca="false">_xlfn.IFNA(IF(COUNTIFS(ZORD!A:A,A3)&gt;1,"Yes",""),"")</f>
         <v>Yes</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="3" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A3,ZORD!A:A,ZORD!C:C),"")</f>
         <v>44926</v>
       </c>
-      <c r="D3" s="10" t="n">
+      <c r="D3" s="11" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A3,ZORD!A:A,ZORD!E:E),"")</f>
         <v>460000003</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="2" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A3,ZORD!A:A,ZORD!D:D),"")</f>
         <v>200000003</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <f aca="false">IF(B3="Yes",_xlfn.XLOOKUP(A3,ZORD!A:A,ZORD!C:C,,,-1),"")</f>
         <v>45657</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="2" t="n">
         <f aca="false">IF(B3="Yes",_xlfn.XLOOKUP(A3,ZORD!A:A,ZORD!E:E,,,-1),"")</f>
         <v>460000005</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="2" t="n">
         <f aca="false">IF(B3="Yes",_xlfn.XLOOKUP(A3,ZORD!A:A,ZORD!D:D,,,-1),"")</f>
         <v>200000005</v>
       </c>
-      <c r="I3" s="11" t="str">
-        <f aca="false" t="array" ref="I3:I3">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(TEXT(IF(A3=ZORD!A:A,ZORD!C:C,""),"DD/MM/YYYY")))</f>
-        <v>31/12/2022,31/12/2024</v>
-      </c>
-      <c r="J3" s="11" t="str">
+      <c r="I3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="12" t="str">
         <f aca="false" t="array" ref="J3:J3">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A3=ZORD!A:A,ZORD!D:D,"")))</f>
         <v>200000003,200000005</v>
       </c>
-      <c r="K3" s="11" t="str">
+      <c r="K3" s="12" t="str">
         <f aca="false" t="array" ref="K3:K3">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A3=ZORD!A:A,ZORD!E:E,"")))</f>
         <v>460000003,460000005</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="str">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2" t="str">
         <f aca="false">_xlfn.IFNA(IF(COUNTIFS(ZORD!A:A,A4)&gt;1,"Yes",""),"")</f>
         <v>Yes</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="3" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A4,ZORD!A:A,ZORD!C:C),"")</f>
         <v>45627</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="11" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A4,ZORD!A:A,ZORD!E:E),"")</f>
         <v>460000004</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="2" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A4,ZORD!A:A,ZORD!D:D),"")</f>
         <v>200000004</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <f aca="false">IF(B4="Yes",_xlfn.XLOOKUP(A4,ZORD!A:A,ZORD!C:C,,,-1),"")</f>
         <v>45657</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="2" t="n">
         <f aca="false">IF(B4="Yes",_xlfn.XLOOKUP(A4,ZORD!A:A,ZORD!E:E,,,-1),"")</f>
         <v>460000006</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="2" t="n">
         <f aca="false">IF(B4="Yes",_xlfn.XLOOKUP(A4,ZORD!A:A,ZORD!D:D,,,-1),"")</f>
         <v>200000006</v>
       </c>
-      <c r="I4" s="11" t="str">
-        <f aca="false" t="array" ref="I4:I4">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(TEXT(IF(A4=ZORD!A:A,ZORD!C:C,""),"DD/MM/YYYY")))</f>
-        <v>01/12/2024,31/12/2024</v>
-      </c>
-      <c r="J4" s="11" t="str">
+      <c r="I4" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="12" t="str">
         <f aca="false" t="array" ref="J4:J4">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A4=ZORD!A:A,ZORD!D:D,"")))</f>
         <v>200000004,200000006</v>
       </c>
-      <c r="K4" s="11" t="str">
+      <c r="K4" s="12" t="str">
         <f aca="false" t="array" ref="K4:K4">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A4=ZORD!A:A,ZORD!E:E,"")))</f>
         <v>460000004,460000006</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="str">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="str">
         <f aca="false">_xlfn.IFNA(IF(COUNTIFS(ZORD!A:A,A5)&gt;1,"Yes",""),"")</f>
         <v/>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="3" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A5,ZORD!A:A,ZORD!C:C),"")</f>
         <v>44926</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="11" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A5,ZORD!A:A,ZORD!E:E),"")</f>
         <v>460000007</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="2" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A5,ZORD!A:A,ZORD!D:D),"")</f>
         <v>200000007</v>
       </c>
-      <c r="F5" s="2" t="str">
+      <c r="F5" s="3" t="str">
         <f aca="false">IF(B5="Yes",_xlfn.XLOOKUP(A5,ZORD!A:A,ZORD!C:C,,,-1),"")</f>
         <v/>
       </c>
-      <c r="G5" s="1" t="str">
+      <c r="G5" s="2" t="str">
         <f aca="false">IF(B5="Yes",_xlfn.XLOOKUP(A5,ZORD!A:A,ZORD!E:E,,,-1),"")</f>
         <v/>
       </c>
-      <c r="H5" s="1" t="str">
+      <c r="H5" s="2" t="str">
         <f aca="false">IF(B5="Yes",_xlfn.XLOOKUP(A5,ZORD!A:A,ZORD!D:D,,,-1),"")</f>
         <v/>
       </c>
-      <c r="I5" s="11" t="str">
-        <f aca="false" t="array" ref="I5:I5">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(TEXT(IF(A5=ZORD!A:A,ZORD!C:C,""),"DD/MM/YYYY")))</f>
-        <v>31/12/2022</v>
-      </c>
-      <c r="J5" s="11" t="str">
+      <c r="I5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="12" t="str">
         <f aca="false" t="array" ref="J5:J5">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A5=ZORD!A:A,ZORD!D:D,"")))</f>
         <v>200000007</v>
       </c>
-      <c r="K5" s="11" t="str">
+      <c r="K5" s="12" t="str">
         <f aca="false" t="array" ref="K5:K5">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A5=ZORD!A:A,ZORD!E:E,"")))</f>
         <v>460000007</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="str">
+      <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="str">
         <f aca="false">_xlfn.IFNA(IF(COUNTIFS(ZORD!A:A,A6)&gt;1,"Yes",""),"")</f>
         <v/>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A6,ZORD!A:A,ZORD!C:C),"")</f>
         <v>44926</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A6,ZORD!A:A,ZORD!E:E),"")</f>
         <v>460000008</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="2" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A6,ZORD!A:A,ZORD!D:D),"")</f>
         <v>200000008</v>
       </c>
-      <c r="F6" s="2" t="str">
+      <c r="F6" s="3" t="str">
         <f aca="false">IF(B6="Yes",_xlfn.XLOOKUP(A6,ZORD!A:A,ZORD!C:C,,,-1),"")</f>
         <v/>
       </c>
-      <c r="G6" s="1" t="str">
+      <c r="G6" s="2" t="str">
         <f aca="false">IF(B6="Yes",_xlfn.XLOOKUP(A6,ZORD!A:A,ZORD!E:E,,,-1),"")</f>
         <v/>
       </c>
-      <c r="H6" s="1" t="str">
+      <c r="H6" s="2" t="str">
         <f aca="false">IF(B6="Yes",_xlfn.XLOOKUP(A6,ZORD!A:A,ZORD!D:D,,,-1),"")</f>
         <v/>
       </c>
-      <c r="I6" s="11" t="str">
-        <f aca="false" t="array" ref="I6:I6">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(TEXT(IF(A6=ZORD!A:A,ZORD!C:C,""),"DD/MM/YYYY")))</f>
-        <v>31/12/2022</v>
-      </c>
-      <c r="J6" s="11" t="str">
+      <c r="I6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="12" t="str">
         <f aca="false" t="array" ref="J6:J6">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A6=ZORD!A:A,ZORD!D:D,"")))</f>
         <v>200000008</v>
       </c>
-      <c r="K6" s="11" t="str">
+      <c r="K6" s="12" t="str">
         <f aca="false" t="array" ref="K6:K6">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A6=ZORD!A:A,ZORD!E:E,"")))</f>
         <v>460000008</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="str">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="str">
         <f aca="false">_xlfn.IFNA(IF(COUNTIFS(ZORD!A:A,A7)&gt;1,"Yes",""),"")</f>
         <v/>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A7,ZORD!A:A,ZORD!C:C),"")</f>
         <v>44926</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="11" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A7,ZORD!A:A,ZORD!E:E),"")</f>
         <v>460000009</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="2" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A7,ZORD!A:A,ZORD!D:D),"")</f>
         <v>200000009</v>
       </c>
-      <c r="F7" s="2" t="str">
+      <c r="F7" s="3" t="str">
         <f aca="false">IF(B7="Yes",_xlfn.XLOOKUP(A7,ZORD!A:A,ZORD!C:C,,,-1),"")</f>
         <v/>
       </c>
-      <c r="G7" s="1" t="str">
+      <c r="G7" s="2" t="str">
         <f aca="false">IF(B7="Yes",_xlfn.XLOOKUP(A7,ZORD!A:A,ZORD!E:E,,,-1),"")</f>
         <v/>
       </c>
-      <c r="H7" s="1" t="str">
+      <c r="H7" s="2" t="str">
         <f aca="false">IF(B7="Yes",_xlfn.XLOOKUP(A7,ZORD!A:A,ZORD!D:D,,,-1),"")</f>
         <v/>
       </c>
-      <c r="I7" s="11" t="str">
-        <f aca="false" t="array" ref="I7:I7">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(TEXT(IF(A7=ZORD!A:A,ZORD!C:C,""),"DD/MM/YYYY")))</f>
-        <v>31/12/2022</v>
-      </c>
-      <c r="J7" s="11" t="str">
+      <c r="I7" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="12" t="str">
         <f aca="false" t="array" ref="J7:J7">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A7=ZORD!A:A,ZORD!D:D,"")))</f>
         <v>200000009</v>
       </c>
-      <c r="K7" s="11" t="str">
+      <c r="K7" s="12" t="str">
         <f aca="false" t="array" ref="K7:K7">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A7=ZORD!A:A,ZORD!E:E,"")))</f>
         <v>460000009</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1" t="str">
+      <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2" t="str">
         <f aca="false">_xlfn.IFNA(IF(COUNTIFS(ZORD!A:A,A8)&gt;1,"Yes",""),"")</f>
         <v/>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="3" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A8,ZORD!A:A,ZORD!C:C),"")</f>
         <v>44926</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A8,ZORD!A:A,ZORD!E:E),"")</f>
         <v>460000010</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="2" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A8,ZORD!A:A,ZORD!D:D),"")</f>
         <v>200000010</v>
       </c>
-      <c r="F8" s="2" t="str">
+      <c r="F8" s="3" t="str">
         <f aca="false">IF(B8="Yes",_xlfn.XLOOKUP(A8,ZORD!A:A,ZORD!C:C,,,-1),"")</f>
         <v/>
       </c>
-      <c r="G8" s="1" t="str">
+      <c r="G8" s="2" t="str">
         <f aca="false">IF(B8="Yes",_xlfn.XLOOKUP(A8,ZORD!A:A,ZORD!E:E,,,-1),"")</f>
         <v/>
       </c>
-      <c r="H8" s="1" t="str">
+      <c r="H8" s="2" t="str">
         <f aca="false">IF(B8="Yes",_xlfn.XLOOKUP(A8,ZORD!A:A,ZORD!D:D,,,-1),"")</f>
         <v/>
       </c>
-      <c r="I8" s="11" t="str">
-        <f aca="false" t="array" ref="I8:I8">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(TEXT(IF(A8=ZORD!A:A,ZORD!C:C,""),"DD/MM/YYYY")))</f>
-        <v>31/12/2022</v>
-      </c>
-      <c r="J8" s="11" t="str">
+      <c r="I8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="12" t="str">
         <f aca="false" t="array" ref="J8:J8">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A8=ZORD!A:A,ZORD!D:D,"")))</f>
         <v>200000010</v>
       </c>
-      <c r="K8" s="11" t="str">
+      <c r="K8" s="12" t="str">
         <f aca="false" t="array" ref="K8:K8">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A8=ZORD!A:A,ZORD!E:E,"")))</f>
         <v>460000010</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1" t="str">
+      <c r="A9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="2" t="str">
         <f aca="false">_xlfn.IFNA(IF(COUNTIFS(ZORD!A:A,A9)&gt;1,"Yes",""),"")</f>
         <v/>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="3" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A9,ZORD!A:A,ZORD!C:C),"")</f>
         <v>44926</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="11" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A9,ZORD!A:A,ZORD!E:E),"")</f>
         <v>460000011</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="2" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A9,ZORD!A:A,ZORD!D:D),"")</f>
         <v>200000011</v>
       </c>
-      <c r="F9" s="2" t="str">
+      <c r="F9" s="3" t="str">
         <f aca="false">IF(B9="Yes",_xlfn.XLOOKUP(A9,ZORD!A:A,ZORD!C:C,,,-1),"")</f>
         <v/>
       </c>
-      <c r="G9" s="1" t="str">
+      <c r="G9" s="2" t="str">
         <f aca="false">IF(B9="Yes",_xlfn.XLOOKUP(A9,ZORD!A:A,ZORD!E:E,,,-1),"")</f>
         <v/>
       </c>
-      <c r="H9" s="1" t="str">
+      <c r="H9" s="2" t="str">
         <f aca="false">IF(B9="Yes",_xlfn.XLOOKUP(A9,ZORD!A:A,ZORD!D:D,,,-1),"")</f>
         <v/>
       </c>
-      <c r="I9" s="11" t="str">
-        <f aca="false" t="array" ref="I9:I9">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(TEXT(IF(A9=ZORD!A:A,ZORD!C:C,""),"DD/MM/YYYY")))</f>
-        <v>31/12/2022</v>
-      </c>
-      <c r="J9" s="11" t="str">
+      <c r="I9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="12" t="str">
         <f aca="false" t="array" ref="J9:J9">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A9=ZORD!A:A,ZORD!D:D,"")))</f>
         <v>200000011</v>
       </c>
-      <c r="K9" s="11" t="str">
+      <c r="K9" s="12" t="str">
         <f aca="false" t="array" ref="K9:K9">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A9=ZORD!A:A,ZORD!E:E,"")))</f>
         <v>460000011</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="str">
+      <c r="A10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="2" t="str">
         <f aca="false">_xlfn.IFNA(IF(COUNTIFS(ZORD!A:A,A10)&gt;1,"Yes",""),"")</f>
         <v/>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="3" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A10,ZORD!A:A,ZORD!C:C),"")</f>
         <v>44926</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="11" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A10,ZORD!A:A,ZORD!E:E),"")</f>
         <v>460000012</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="2" t="n">
         <f aca="false">_xlfn.IFNA(_xlfn.XLOOKUP(A10,ZORD!A:A,ZORD!D:D),"")</f>
         <v>200000012</v>
       </c>
-      <c r="F10" s="2" t="str">
+      <c r="F10" s="3" t="str">
         <f aca="false">IF(B10="Yes",_xlfn.XLOOKUP(A10,ZORD!A:A,ZORD!C:C,,,-1),"")</f>
         <v/>
       </c>
-      <c r="G10" s="1" t="str">
+      <c r="G10" s="2" t="str">
         <f aca="false">IF(B10="Yes",_xlfn.XLOOKUP(A10,ZORD!A:A,ZORD!E:E,,,-1),"")</f>
         <v/>
       </c>
-      <c r="H10" s="1" t="str">
+      <c r="H10" s="2" t="str">
         <f aca="false">IF(B10="Yes",_xlfn.XLOOKUP(A10,ZORD!A:A,ZORD!D:D,,,-1),"")</f>
         <v/>
       </c>
-      <c r="I10" s="11" t="str">
-        <f aca="false" t="array" ref="I10:I10">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(TEXT(IF(A10=ZORD!A:A,ZORD!C:C,""),"DD/MM/YYYY")))</f>
-        <v>31/12/2022</v>
-      </c>
-      <c r="J10" s="11" t="str">
+      <c r="I10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="12" t="str">
         <f aca="false" t="array" ref="J10:J10">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A10=ZORD!A:A,ZORD!D:D,"")))</f>
         <v>200000012</v>
       </c>
-      <c r="K10" s="11" t="str">
+      <c r="K10" s="12" t="str">
         <f aca="false" t="array" ref="K10:K10">_xlfn.TEXTJOIN(",",TRUE(),_xlfn.UNIQUE(IF(A10=ZORD!A:A,ZORD!E:E,"")))</f>
         <v>460000012</v>
       </c>
@@ -1040,263 +1047,263 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="12" t="n">
+        <v>44622</v>
+      </c>
+      <c r="C2" s="12" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>200000001</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>460000001</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>45657</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>200000002</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>460000002</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>44568</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>45291</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>460000000</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>44926</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>200000003</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>460000003</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>44470</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>45627</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>200000004</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>460000004</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>44470</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>45657</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>200000005</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>460000005</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>44470</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>45657</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>200000006</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>460000006</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>44375</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>44926</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>200000007</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>460000007</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>44926</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>200000008</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>460000008</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B11" s="12" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>44926</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>200000009</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>460000009</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="B12" s="12" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>44926</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>200000010</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>460000010</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="B13" s="12" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>44926</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>200000011</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>460000011</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="11" t="n">
-        <v>44622</v>
-      </c>
-      <c r="C2" s="11" t="n">
-        <v>46022</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>200000001</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>460000001</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="11" t="n">
+      <c r="B14" s="12" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>44926</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>200000012</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>460000012</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="12" t="n">
         <v>44197</v>
       </c>
-      <c r="C3" s="11" t="n">
-        <v>45657</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>200000002</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>460000002</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="11" t="n">
-        <v>44568</v>
-      </c>
-      <c r="C4" s="11" t="n">
+      <c r="C15" s="12" t="n">
         <v>45291</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>200000000</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>460000000</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="11" t="n">
-        <v>44197</v>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>44926</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>200000003</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>460000003</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="11" t="n">
-        <v>44470</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>45627</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>200000004</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>460000004</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>44470</v>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>45657</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>200000005</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>460000005</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="11" t="n">
-        <v>44470</v>
-      </c>
-      <c r="C8" s="11" t="n">
-        <v>45657</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>200000006</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>460000006</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>44375</v>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>44926</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>200000007</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>460000007</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v>43831</v>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>44926</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>200000008</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>460000008</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="11" t="n">
-        <v>43831</v>
-      </c>
-      <c r="C11" s="11" t="n">
-        <v>44926</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>200000009</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>460000009</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="11" t="n">
-        <v>43831</v>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>44926</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>200000010</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>460000010</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>43831</v>
-      </c>
-      <c r="C13" s="11" t="n">
-        <v>44926</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>200000011</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>460000011</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="11" t="n">
-        <v>43831</v>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>44926</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>200000012</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>460000012</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="11" t="n">
-        <v>44197</v>
-      </c>
-      <c r="C15" s="11" t="n">
-        <v>45291</v>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="D15" s="2" t="n">
         <v>200000013</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="2" t="n">
         <v>460000013</v>
       </c>
     </row>
